--- a/DataAugmentationResult.xlsx
+++ b/DataAugmentationResult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\ADA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5126EAE-6866-449D-95B7-E14A4706926E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A7B3A9-6E70-4B6E-8A4B-975B9B249BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2010" windowWidth="29040" windowHeight="15720" xr2:uid="{3BB353AA-44C7-499C-B64C-BB9FF7C08163}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>Augmentation</t>
   </si>
@@ -45,9 +45,6 @@
     <t>F1-Score</t>
   </si>
   <si>
-    <t>delta Baseline</t>
-  </si>
-  <si>
     <t>Rotation (+-15°)</t>
   </si>
   <si>
@@ -57,7 +54,16 @@
     <t>Rotation (+-10°)</t>
   </si>
   <si>
-    <t>Width and Height shift (0.1)</t>
+    <t>Horizontal and vertical flip</t>
+  </si>
+  <si>
+    <t>Width and height shift (0.1)</t>
+  </si>
+  <si>
+    <t>10 Epochen</t>
+  </si>
+  <si>
+    <t>20 Epochen</t>
   </si>
 </sst>
 </file>
@@ -108,7 +114,67 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="9"/>
@@ -459,13 +525,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F8A3B8-6197-4096-80B6-9BEC46D59AEE}">
-  <dimension ref="C6:H18"/>
+  <dimension ref="C4:P20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,199 +557,459 @@
       <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="K6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.96399999999999997</v>
+        <v>0.96140000000000003</v>
       </c>
       <c r="F8">
-        <v>0.98109999999999997</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="G8">
-        <v>0.95320000000000005</v>
+        <v>0.97729999999999995</v>
       </c>
       <c r="H8">
-        <v>0.96689999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0.9667</v>
+      </c>
+      <c r="N8">
+        <v>0.97560000000000002</v>
+      </c>
+      <c r="O8">
+        <v>0.96379999999999999</v>
+      </c>
+      <c r="P8">
+        <v>0.96960000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>0.95979999999999999</v>
+        <v>0.96489999999999998</v>
       </c>
       <c r="F10">
-        <v>0.96919999999999995</v>
+        <v>0.97970000000000002</v>
       </c>
       <c r="G10">
-        <v>0.95779999999999998</v>
+        <v>0.95630000000000004</v>
       </c>
       <c r="H10">
-        <v>0.96340000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
+        <v>0.96789999999999998</v>
+      </c>
+      <c r="K10" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10">
+        <v>0.96409999999999996</v>
+      </c>
+      <c r="N10">
+        <v>0.97050000000000003</v>
+      </c>
+      <c r="O10">
+        <v>0.96440000000000003</v>
+      </c>
+      <c r="P10">
+        <v>0.96740000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E11">
         <f>E10-E$8</f>
-        <v>-4.1999999999999815E-3</v>
+        <v>3.4999999999999476E-3</v>
       </c>
       <c r="F11">
         <f>F10-F$8</f>
-        <v>-1.1900000000000022E-2</v>
+        <v>2.5700000000000056E-2</v>
       </c>
       <c r="G11">
         <f>G10-G$8</f>
-        <v>4.5999999999999375E-3</v>
+        <v>-2.0999999999999908E-2</v>
       </c>
       <c r="H11">
         <f>H10-H$8</f>
-        <v>-3.4999999999999476E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+        <v>2.3999999999999577E-3</v>
+      </c>
+      <c r="M11">
+        <f>M10-M$8</f>
+        <v>-2.6000000000000467E-3</v>
+      </c>
+      <c r="N11">
+        <f>N10-N$8</f>
+        <v>-5.0999999999999934E-3</v>
+      </c>
+      <c r="O11">
+        <f>O10-O$8</f>
+        <v>6.0000000000004494E-4</v>
+      </c>
+      <c r="P11">
+        <f>P10-P$8</f>
+        <v>-2.1999999999999797E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>0.96050000000000002</v>
+        <v>0.94289999999999996</v>
       </c>
       <c r="F12">
-        <v>0.96699999999999997</v>
+        <v>0.95609999999999995</v>
       </c>
       <c r="G12">
-        <v>0.96120000000000005</v>
+        <v>0.93969999999999998</v>
       </c>
       <c r="H12">
-        <v>0.96409999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
+        <v>0.94779999999999998</v>
+      </c>
+      <c r="K12" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12">
+        <v>0.9637</v>
+      </c>
+      <c r="N12">
+        <v>0.97240000000000004</v>
+      </c>
+      <c r="O12">
+        <v>0.96150000000000002</v>
+      </c>
+      <c r="P12">
+        <v>0.96689999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E13">
         <f>E12-E$8</f>
-        <v>-3.4999999999999476E-3</v>
+        <v>-1.8500000000000072E-2</v>
       </c>
       <c r="F13">
         <f>F12-F$8</f>
-        <v>-1.4100000000000001E-2</v>
+        <v>2.0999999999999908E-3</v>
       </c>
       <c r="G13">
         <f>G12-G$8</f>
-        <v>8.0000000000000071E-3</v>
+        <v>-3.7599999999999967E-2</v>
       </c>
       <c r="H13">
         <f>H12-H$8</f>
-        <v>-2.8000000000000247E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+        <v>-1.7700000000000049E-2</v>
+      </c>
+      <c r="M13">
+        <f>M12-M$8</f>
+        <v>-3.0000000000000027E-3</v>
+      </c>
+      <c r="N13">
+        <f>N12-N$8</f>
+        <v>-3.1999999999999806E-3</v>
+      </c>
+      <c r="O13">
+        <f>O12-O$8</f>
+        <v>-2.2999999999999687E-3</v>
+      </c>
+      <c r="P13">
+        <f>P12-P$8</f>
+        <v>-2.7000000000000357E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>0.95440000000000003</v>
+        <v>0.95920000000000005</v>
       </c>
       <c r="F14">
-        <v>0.98219999999999996</v>
+        <v>0.97160000000000002</v>
       </c>
       <c r="G14">
-        <v>0.9345</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="H14">
-        <v>0.9577</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+        <v>0.9627</v>
+      </c>
+      <c r="K14" t="s">
         <v>6</v>
       </c>
+      <c r="M14">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="N14">
+        <v>0.96030000000000004</v>
+      </c>
+      <c r="O14">
+        <v>0.9657</v>
+      </c>
+      <c r="P14">
+        <v>0.96299999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E15">
         <f>E14-E$8</f>
-        <v>-9.5999999999999419E-3</v>
+        <v>-2.1999999999999797E-3</v>
       </c>
       <c r="F15">
         <f>F14-F$8</f>
-        <v>1.0999999999999899E-3</v>
+        <v>1.760000000000006E-2</v>
       </c>
       <c r="G15">
         <f>G14-G$8</f>
-        <v>-1.870000000000005E-2</v>
+        <v>-2.3299999999999987E-2</v>
       </c>
       <c r="H15">
         <f>H14-H$8</f>
-        <v>-9.199999999999986E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+        <v>-2.8000000000000247E-3</v>
+      </c>
+      <c r="M15">
+        <f>M14-M$8</f>
+        <v>-7.7000000000000401E-3</v>
+      </c>
+      <c r="N15">
+        <f>N14-N$8</f>
+        <v>-1.529999999999998E-2</v>
+      </c>
+      <c r="O15">
+        <f>O14-O$8</f>
+        <v>1.9000000000000128E-3</v>
+      </c>
+      <c r="P15">
+        <f>P14-P$8</f>
+        <v>-6.6000000000000503E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="E17">
-        <v>0.9617</v>
+        <v>0.95620000000000005</v>
       </c>
       <c r="F17">
-        <v>0.96440000000000003</v>
+        <v>0.95079999999999998</v>
       </c>
       <c r="G17">
-        <v>0.96640000000000004</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="H17">
-        <v>0.96540000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.96079999999999999</v>
+      </c>
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>0.96709999999999996</v>
+      </c>
+      <c r="N17">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="O17">
+        <v>0.9698</v>
+      </c>
+      <c r="P17">
+        <v>0.97019999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E18">
         <f>E17-E$8</f>
-        <v>-2.2999999999999687E-3</v>
+        <v>-5.1999999999999824E-3</v>
       </c>
       <c r="F18">
         <f>F17-F$8</f>
-        <v>-1.6699999999999937E-2</v>
+        <v>-3.1999999999999806E-3</v>
       </c>
       <c r="G18">
         <f>G17-G$8</f>
-        <v>1.319999999999999E-2</v>
+        <v>-6.2999999999999723E-3</v>
       </c>
       <c r="H18">
         <f>H17-H$8</f>
-        <v>-1.4999999999999458E-3</v>
+        <v>-4.7000000000000375E-3</v>
+      </c>
+      <c r="M18">
+        <f>M17-M$8</f>
+        <v>3.9999999999995595E-4</v>
+      </c>
+      <c r="N18">
+        <f>N17-N$8</f>
+        <v>-4.9000000000000155E-3</v>
+      </c>
+      <c r="O18">
+        <f>O17-O$8</f>
+        <v>6.0000000000000053E-3</v>
+      </c>
+      <c r="P18">
+        <f>P17-P$8</f>
+        <v>5.9999999999993392E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19">
+        <v>0.96430000000000005</v>
+      </c>
+      <c r="F19">
+        <v>0.97629999999999995</v>
+      </c>
+      <c r="G19">
+        <v>0.95860000000000001</v>
+      </c>
+      <c r="H19">
+        <v>0.96740000000000004</v>
+      </c>
+      <c r="K19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M19">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="N19">
+        <v>0.97</v>
+      </c>
+      <c r="O19">
+        <v>0.97409999999999997</v>
+      </c>
+      <c r="P19">
+        <v>0.97199999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <f>E19-E$8</f>
+        <v>2.9000000000000137E-3</v>
+      </c>
+      <c r="F20">
+        <f>F19-F$8</f>
+        <v>2.2299999999999986E-2</v>
+      </c>
+      <c r="G20">
+        <f>G19-G$8</f>
+        <v>-1.8699999999999939E-2</v>
+      </c>
+      <c r="H20">
+        <f>H19-H$8</f>
+        <v>1.9000000000000128E-3</v>
+      </c>
+      <c r="M20">
+        <f>M19-M$8</f>
+        <v>2.2999999999999687E-3</v>
+      </c>
+      <c r="N20">
+        <f>N19-N$8</f>
+        <v>-5.6000000000000494E-3</v>
+      </c>
+      <c r="O20">
+        <f>O19-O$8</f>
+        <v>1.0299999999999976E-2</v>
+      </c>
+      <c r="P20">
+        <f>P19-P$8</f>
+        <v>2.3999999999999577E-3</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E11:H11">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:H13">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="15" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:H15">
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="25" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:H18">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:H20">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:P11">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13:P13">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15:P15">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18:P18">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20:P20">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/DataAugmentationResult.xlsx
+++ b/DataAugmentationResult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\ADA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A7B3A9-6E70-4B6E-8A4B-975B9B249BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E068521A-1F85-4CC8-A44A-4D9BB57C5B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2010" windowWidth="29040" windowHeight="15720" xr2:uid="{3BB353AA-44C7-499C-B64C-BB9FF7C08163}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BB353AA-44C7-499C-B64C-BB9FF7C08163}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>Augmentation</t>
   </si>
@@ -64,6 +64,31 @@
   </si>
   <si>
     <t>20 Epochen</t>
+  </si>
+  <si>
+    <t>Rotation(+-5°)
+Width and height shift (0.1)
+Horizontal and vertical flip</t>
+  </si>
+  <si>
+    <t>Models getestet auf Augmentierten Testdaten</t>
+  </si>
+  <si>
+    <t>Baseline - augmentierte Daten</t>
+  </si>
+  <si>
+    <t>Baseline - Standard Daten</t>
+  </si>
+  <si>
+    <t>Kombination* - Standard Daten</t>
+  </si>
+  <si>
+    <t>Kombination* - augmentierte Daten</t>
+  </si>
+  <si>
+    <t>* Rotation(+-5°)
+Width and height shift (0.1)
+Horizontal and vertical flip</t>
   </si>
 </sst>
 </file>
@@ -107,14 +132,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="9"/>
@@ -525,10 +628,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F8A3B8-6197-4096-80B6-9BEC46D59AEE}">
-  <dimension ref="C4:P20"/>
+  <dimension ref="C4:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
     <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -579,16 +682,16 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.96140000000000003</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="F8">
-        <v>0.95399999999999996</v>
+        <v>0.97009999999999996</v>
       </c>
       <c r="G8">
-        <v>0.97729999999999995</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="H8">
-        <v>0.96550000000000002</v>
+        <v>0.96919999999999995</v>
       </c>
       <c r="K8" t="s">
         <v>1</v>
@@ -611,16 +714,16 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>0.96489999999999998</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="F10">
-        <v>0.97970000000000002</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G10">
-        <v>0.95630000000000004</v>
+        <v>0.95369999999999999</v>
       </c>
       <c r="H10">
-        <v>0.96789999999999998</v>
+        <v>0.96430000000000005</v>
       </c>
       <c r="K10" t="s">
         <v>7</v>
@@ -641,19 +744,19 @@
     <row r="11" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E11">
         <f>E10-E$8</f>
-        <v>3.4999999999999476E-3</v>
+        <v>-5.0000000000000044E-3</v>
       </c>
       <c r="F11">
         <f>F10-F$8</f>
-        <v>2.5700000000000056E-2</v>
+        <v>4.9000000000000155E-3</v>
       </c>
       <c r="G11">
         <f>G10-G$8</f>
-        <v>-2.0999999999999908E-2</v>
+        <v>-1.4700000000000046E-2</v>
       </c>
       <c r="H11">
         <f>H10-H$8</f>
-        <v>2.3999999999999577E-3</v>
+        <v>-4.8999999999999044E-3</v>
       </c>
       <c r="M11">
         <f>M10-M$8</f>
@@ -707,19 +810,19 @@
     <row r="13" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E13">
         <f>E12-E$8</f>
-        <v>-1.8500000000000072E-2</v>
+        <v>-2.3100000000000009E-2</v>
       </c>
       <c r="F13">
         <f>F12-F$8</f>
-        <v>2.0999999999999908E-3</v>
+        <v>-1.4000000000000012E-2</v>
       </c>
       <c r="G13">
         <f>G12-G$8</f>
-        <v>-3.7599999999999967E-2</v>
+        <v>-2.8700000000000059E-2</v>
       </c>
       <c r="H13">
         <f>H12-H$8</f>
-        <v>-1.7700000000000049E-2</v>
+        <v>-2.1399999999999975E-2</v>
       </c>
       <c r="M13">
         <f>M12-M$8</f>
@@ -773,19 +876,19 @@
     <row r="15" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E15">
         <f>E14-E$8</f>
-        <v>-2.1999999999999797E-3</v>
+        <v>-6.7999999999999172E-3</v>
       </c>
       <c r="F15">
         <f>F14-F$8</f>
-        <v>1.760000000000006E-2</v>
+        <v>1.5000000000000568E-3</v>
       </c>
       <c r="G15">
         <f>G14-G$8</f>
-        <v>-2.3299999999999987E-2</v>
+        <v>-1.4400000000000079E-2</v>
       </c>
       <c r="H15">
         <f>H14-H$8</f>
-        <v>-2.8000000000000247E-3</v>
+        <v>-6.4999999999999503E-3</v>
       </c>
       <c r="M15">
         <f>M14-M$8</f>
@@ -839,19 +942,19 @@
     <row r="18" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E18">
         <f>E17-E$8</f>
-        <v>-5.1999999999999824E-3</v>
+        <v>-9.7999999999999199E-3</v>
       </c>
       <c r="F18">
         <f>F17-F$8</f>
-        <v>-3.1999999999999806E-3</v>
+        <v>-1.9299999999999984E-2</v>
       </c>
       <c r="G18">
         <f>G17-G$8</f>
-        <v>-6.2999999999999723E-3</v>
+        <v>2.5999999999999357E-3</v>
       </c>
       <c r="H18">
         <f>H17-H$8</f>
-        <v>-4.7000000000000375E-3</v>
+        <v>-8.3999999999999631E-3</v>
       </c>
       <c r="M18">
         <f>M17-M$8</f>
@@ -905,19 +1008,19 @@
     <row r="20" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E20">
         <f>E19-E$8</f>
-        <v>2.9000000000000137E-3</v>
+        <v>-1.6999999999999238E-3</v>
       </c>
       <c r="F20">
         <f>F19-F$8</f>
-        <v>2.2299999999999986E-2</v>
+        <v>6.1999999999999833E-3</v>
       </c>
       <c r="G20">
         <f>G19-G$8</f>
-        <v>-1.8699999999999939E-2</v>
+        <v>-9.8000000000000309E-3</v>
       </c>
       <c r="H20">
         <f>H19-H$8</f>
-        <v>1.9000000000000128E-3</v>
+        <v>-1.7999999999999128E-3</v>
       </c>
       <c r="M20">
         <f>M19-M$8</f>
@@ -936,80 +1039,264 @@
         <v>2.3999999999999577E-3</v>
       </c>
     </row>
+    <row r="22" spans="3:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="F22">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="G22">
+        <v>0.9083</v>
+      </c>
+      <c r="H22">
+        <v>0.94510000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <f>E22-E$8</f>
+        <v>-2.4299999999999988E-2</v>
+      </c>
+      <c r="F23">
+        <f>F22-F$8</f>
+        <v>1.4900000000000024E-2</v>
+      </c>
+      <c r="G23">
+        <f>G22-G$8</f>
+        <v>-6.0100000000000042E-2</v>
+      </c>
+      <c r="H23">
+        <f>H22-H$8</f>
+        <v>-2.4099999999999899E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31">
+        <v>0.96140000000000003</v>
+      </c>
+      <c r="F31">
+        <v>0.97560000000000002</v>
+      </c>
+      <c r="G31">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="H31">
+        <v>0.9647</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32">
+        <v>0.8962</v>
+      </c>
+      <c r="F32">
+        <v>0.86119999999999997</v>
+      </c>
+      <c r="G32">
+        <v>0.96809999999999996</v>
+      </c>
+      <c r="H32">
+        <v>0.91149999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <f>E32-E$31</f>
+        <v>-6.5200000000000036E-2</v>
+      </c>
+      <c r="F33">
+        <f t="shared" ref="F33:H33" si="0">F32-F$31</f>
+        <v>-0.11440000000000006</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>1.4100000000000001E-2</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>-5.3200000000000025E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="F36">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="G36">
+        <v>0.9083</v>
+      </c>
+      <c r="H36">
+        <v>0.94510000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37">
+        <v>0.96109999999999995</v>
+      </c>
+      <c r="F37">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="G37">
+        <v>0.96409999999999996</v>
+      </c>
+      <c r="H37">
+        <v>0.96479999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E38">
+        <f>E37-E$36</f>
+        <v>1.9399999999999973E-2</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ref="F38:H38" si="1">F37-F$36</f>
+        <v>-1.9499999999999962E-2</v>
+      </c>
+      <c r="G38">
+        <f>G37-G$36</f>
+        <v>5.5799999999999961E-2</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>1.969999999999994E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C40" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E11:H11">
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="32" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="33" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:H13">
-    <cfRule type="cellIs" dxfId="17" priority="15" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="30" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="31" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:H15">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="40" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="41" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:H18">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="28" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="29" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:H20">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="26" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:P11">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="22" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:P13">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15:P15">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="24" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="25" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:P18">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:P20">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9:P9">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
+      <formula>0.00405</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:H23">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33:H33">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:H38">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -1018,5 +1305,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DataAugmentationResult.xlsx
+++ b/DataAugmentationResult.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\ADA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E068521A-1F85-4CC8-A44A-4D9BB57C5B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AD5CC8-B514-470B-BEEA-AE93D02A7382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BB353AA-44C7-499C-B64C-BB9FF7C08163}"/>
   </bookViews>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>Augmentation</t>
   </si>
@@ -89,6 +100,9 @@
     <t>* Rotation(+-5°)
 Width and height shift (0.1)
 Horizontal and vertical flip</t>
+  </si>
+  <si>
+    <t>Brightness [0.8, 1.2]</t>
   </si>
 </sst>
 </file>
@@ -142,7 +156,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="31">
     <dxf>
       <font>
         <color theme="9"/>
@@ -175,62 +189,42 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF92D050"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
       </font>
     </dxf>
     <dxf>
@@ -332,9 +326,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -372,7 +366,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -478,7 +472,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -620,7 +614,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1039,95 +1033,130 @@
         <v>2.3999999999999577E-3</v>
       </c>
     </row>
-    <row r="22" spans="3:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
-        <v>13</v>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>20</v>
       </c>
       <c r="E22">
-        <v>0.94169999999999998</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="F22">
-        <v>0.98499999999999999</v>
+        <v>0.62860000000000005</v>
       </c>
       <c r="G22">
-        <v>0.9083</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="H22">
-        <v>0.94510000000000005</v>
+        <v>0.76590000000000003</v>
       </c>
     </row>
     <row r="23" spans="3:16" x14ac:dyDescent="0.25">
       <c r="E23">
         <f>E22-E$8</f>
-        <v>-2.4299999999999988E-2</v>
+        <v>-0.29699999999999993</v>
       </c>
       <c r="F23">
         <f>F22-F$8</f>
-        <v>1.4900000000000024E-2</v>
+        <v>-0.34149999999999991</v>
       </c>
       <c r="G23">
         <f>G22-G$8</f>
-        <v>-6.0100000000000042E-2</v>
+        <v>1.1499999999999955E-2</v>
       </c>
       <c r="H23">
         <f>H22-H$8</f>
+        <v>-0.20329999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="F24">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="G24">
+        <v>0.9083</v>
+      </c>
+      <c r="H24">
+        <v>0.94510000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <f>E24-E$8</f>
+        <v>-2.4299999999999988E-2</v>
+      </c>
+      <c r="F25">
+        <f>F24-F$8</f>
+        <v>1.4900000000000024E-2</v>
+      </c>
+      <c r="G25">
+        <f>G24-G$8</f>
+        <v>-6.0100000000000042E-2</v>
+      </c>
+      <c r="H25">
+        <f>H24-H$8</f>
         <v>-2.4099999999999899E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="31" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>16</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>0.96140000000000003</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>0.97560000000000002</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>0.95399999999999996</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>0.9647</v>
       </c>
     </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>0.8962</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <v>0.86119999999999997</v>
       </c>
-      <c r="G32">
+      <c r="G34">
         <v>0.96809999999999996</v>
       </c>
-      <c r="H32">
+      <c r="H34">
         <v>0.91149999999999998</v>
       </c>
     </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="E33">
-        <f>E32-E$31</f>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <f>E34-E$33</f>
         <v>-6.5200000000000036E-2</v>
       </c>
-      <c r="F33">
-        <f t="shared" ref="F33:H33" si="0">F32-F$31</f>
+      <c r="F35">
+        <f>F34-F$33</f>
         <v>-0.11440000000000006</v>
       </c>
-      <c r="G33">
-        <f t="shared" si="0"/>
+      <c r="G35">
+        <f>G34-G$33</f>
         <v>1.4100000000000001E-2</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="0"/>
+      <c r="H35">
+        <f>H34-H$33</f>
         <v>-5.3200000000000025E-2</v>
       </c>
     </row>
@@ -1171,7 +1200,7 @@
         <v>1.9399999999999973E-2</v>
       </c>
       <c r="F38">
-        <f t="shared" ref="F38:H38" si="1">F37-F$36</f>
+        <f t="shared" ref="F38:H38" si="0">F37-F$36</f>
         <v>-1.9499999999999962E-2</v>
       </c>
       <c r="G38">
@@ -1179,7 +1208,7 @@
         <v>5.5799999999999961E-2</v>
       </c>
       <c r="H38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.969999999999994E-2</v>
       </c>
     </row>
@@ -1190,113 +1219,121 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E11:H11">
-    <cfRule type="cellIs" dxfId="34" priority="32" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="34" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="35" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:H13">
-    <cfRule type="cellIs" dxfId="32" priority="30" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="33" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:H15">
-    <cfRule type="cellIs" dxfId="30" priority="40" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="41" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="42" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:H18">
-    <cfRule type="cellIs" dxfId="28" priority="28" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="31" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:H20">
-    <cfRule type="cellIs" dxfId="26" priority="26" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="27" operator="greaterThan">
-      <formula>0</formula>
+    <cfRule type="cellIs" dxfId="22" priority="28" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="29" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:H25">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35:H35">
+    <cfRule type="cellIs" dxfId="18" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:H38">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9:P9">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="greaterThan">
+      <formula>0.00405</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:P11">
-    <cfRule type="cellIs" dxfId="24" priority="22" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="24" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="25" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:P13">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="22" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="23" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15:P15">
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="26" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:P18">
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:P20">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M9:P9">
-    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
-      <formula>0.00405</formula>
+    <cfRule type="cellIs" dxfId="3" priority="18" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="19" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23:H23">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E33:H33">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E38:H38">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
